--- a/docs/xlsx/jobs-2026-10-18.xlsx
+++ b/docs/xlsx/jobs-2026-10-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,67 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>East Coast Staff Investigator</t>
+  </si>
+  <si>
+    <t>The Exoneration Project</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21ee30a92d1f4fcfae4fe0ff6c587675-east-coast-staff-investigator-the-exoneration-project-new-york</t>
+  </si>
+  <si>
+    <t>Facility Associate</t>
+  </si>
+  <si>
+    <t>The Mountaineers</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9205abe0dede4817bdc16ebadac0f0ea-facility-associate-the-mountaineers-seattle</t>
+  </si>
+  <si>
+    <t>Grants Database Manager</t>
+  </si>
+  <si>
+    <t>DC Bar Foundation</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e2dd137a38cd4f2a9491181ad8623362-grants-database-manager-dc-bar-foundation-washington</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +108,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +134,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +573,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +612,82 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-18.xlsx
+++ b/docs/xlsx/jobs-2026-10-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="50">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,27 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Admin and Finance Manager</t>
+  </si>
+  <si>
+    <t>Seattle REconomy</t>
+  </si>
+  <si>
+    <t>Shoreline, Washington</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Environment, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e57fe9b0766f4b57b9d4a0581fa557e0-admin-and-finance-manager-seattle-reconomy-shoreline</t>
+  </si>
+  <si>
     <t>East Coast Staff Investigator</t>
   </si>
   <si>
@@ -49,9 +70,6 @@
     <t>New York, New York</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -61,6 +79,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/21ee30a92d1f4fcfae4fe0ff6c587675-east-coast-staff-investigator-the-exoneration-project-new-york</t>
   </si>
   <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>NEIGHBORHOOD COUNSELING AND COMMUNITY SERVICES INC</t>
+  </si>
+  <si>
+    <t>N Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Children Youth, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37aed2135d214d3bad5f17ae100da153-executive-director-neighborhood-counseling-and-community-services-inc-n-cambridge</t>
+  </si>
+  <si>
     <t>Facility Associate</t>
   </si>
   <si>
@@ -70,9 +109,6 @@
     <t>Seattle, WA</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 22.00 - 25.50/hour</t>
   </si>
   <si>
@@ -82,6 +118,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9205abe0dede4817bdc16ebadac0f0ea-facility-associate-the-mountaineers-seattle</t>
   </si>
   <si>
+    <t>GARE Network Impact Analyst (Part-Time)</t>
+  </si>
+  <si>
+    <t>Race Forward</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 39.00 - 41.00/hour</t>
+  </si>
+  <si>
+    <t>Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38ea31afba5f447aa1e33f9189373a63-gare-network-impact-analyst-part-time-race-forward-new-york</t>
+  </si>
+  <si>
     <t>Grants Database Manager</t>
   </si>
   <si>
@@ -92,6 +146,24 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/e2dd137a38cd4f2a9491181ad8623362-grants-database-manager-dc-bar-foundation-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator role: Love Languages &amp; Cultures? Lead a Global Community of Teachers, Interns &amp; Volunteers! DC's #1-Rated Language Classes</t>
+  </si>
+  <si>
+    <t>Global Language Network</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 43000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3827f706a96a42b6b98a293826cad21b-program-coordinator-role-love-languages-cultures-lead-a-global-community-of-teachers-interns-volunteers-dcs-1-rated-language-classes-global-language-network-washington</t>
   </si>
 </sst>
 </file>
@@ -573,7 +645,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -646,39 +718,131 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>25</v>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -687,6 +851,10 @@
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
